--- a/checklists/excel/peer/functionality.xlsx
+++ b/checklists/excel/peer/functionality.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Functionality" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functionality Review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,94 +425,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item Text</t>
+          <t>Sr.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Main Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to Measure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Requirements are correctly implemented (MUST)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Functionality Review</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>All user stories addressed; Acceptance criteria met; Edge cases handled</t>
+          <t>Verify requirements implementation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Verify that all requirements have been properly implemented</t>
+          <t>Ensure all user stories and acceptance criteria have been properly implemented.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>All acceptance criteria met and user stories completed</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Review against user story acceptance criteria</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Code follows established patterns and conventions (GOOD)</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Functionality Review</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Architecture patterns followed; Design patterns applied; Code style consistent</t>
+          <t>Check business logic correctness</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Code should follow established architectural and design patterns</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Performance considerations are addressed (GOOD)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Database queries optimized; Memory usage reasonable; Response times acceptable</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Code should perform well under expected load conditions</t>
+          <t>Verify that business logic is implemented correctly and handles all business rules.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Business rules implemented as per requirements</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Unit tests and integration tests</t>
         </is>
       </c>
     </row>
